--- a/artfynd/A 19961-2022 artfynd.xlsx
+++ b/artfynd/A 19961-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19961-2022 artfynd.xlsx
+++ b/artfynd/A 19961-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107781750</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>NVI Aros Park</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107679001</t>
         </is>
       </c>
     </row>
@@ -1001,6 +1016,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698806</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/169068</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107679086</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1335,6 +1365,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107679099</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>NVI Aros Park</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107679112</t>
         </is>
       </c>
     </row>
@@ -1549,6 +1589,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107678929</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1654,6 +1699,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107678983</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1759,6 +1809,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107679030</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1864,6 +1919,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698730</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1974,6 +2034,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698712</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2079,6 +2144,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107780930</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2202,6 +2272,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>Uppföljning av skyddade områden</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/441710</t>
         </is>
       </c>
     </row>
@@ -2309,6 +2384,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107678914</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2414,6 +2494,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107678916</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2519,6 +2604,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107678920</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2624,6 +2714,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107678942</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2729,6 +2824,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107678988</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2834,6 +2934,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107678993</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2939,6 +3044,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107679071</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3057,6 +3167,11 @@
       <c r="AY23" t="inlineStr">
         <is>
           <t>Uppföljning av skyddade områden</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1014476</t>
         </is>
       </c>
     </row>
@@ -3162,6 +3277,11 @@
       <c r="AY24" t="inlineStr">
         <is>
           <t>NVI Aros Park</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107678986</t>
         </is>
       </c>
     </row>
@@ -3270,6 +3390,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107782606</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3375,6 +3500,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107781220</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3493,6 +3623,11 @@
       <c r="AY27" t="inlineStr">
         <is>
           <t>Uppföljning av skyddade områden</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1070677</t>
         </is>
       </c>
     </row>
@@ -3600,6 +3735,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107678902</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3705,6 +3845,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107678907</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3810,6 +3955,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107678952</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3915,6 +4065,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107679009</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4020,6 +4175,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107679021</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4125,6 +4285,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107780955</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4241,6 +4406,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1353520</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4355,6 +4525,11 @@
       <c r="AY35" t="inlineStr">
         <is>
           <t>Uppföljning av skyddade områden</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1353521</t>
         </is>
       </c>
     </row>
@@ -4462,6 +4637,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698825</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4567,6 +4747,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107781562</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4672,6 +4857,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107781572</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4777,6 +4967,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698831</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4882,6 +5077,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698832</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4987,6 +5187,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107780980</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5092,6 +5297,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107781004</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5197,6 +5407,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107781782</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5302,6 +5517,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698834</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5407,6 +5627,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107782222</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5512,6 +5737,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107782233</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5617,6 +5847,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107782261</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5722,6 +5957,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107783704</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5827,6 +6067,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698790</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5932,6 +6177,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107782337</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6046,6 +6296,11 @@
       <c r="AY51" t="inlineStr">
         <is>
           <t>Uppföljning av skyddade områden</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1614860</t>
         </is>
       </c>
     </row>
@@ -6153,6 +6408,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698733</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6258,6 +6518,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107781064</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6363,6 +6628,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107781092</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6468,6 +6738,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107781116</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6571,6 +6846,11 @@
       <c r="AY56" t="inlineStr">
         <is>
           <t>NVI Aros Park</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107782279</t>
         </is>
       </c>
     </row>
@@ -6680,6 +6960,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107698793</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6787,6 +7072,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107782396</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6893,6 +7183,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107782676</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6997,6 +7292,11 @@
       <c r="AY60" t="inlineStr">
         <is>
           <t>NVI Aros Park</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107783606</t>
         </is>
       </c>
     </row>
@@ -7101,6 +7401,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107782638</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7203,6 +7508,11 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107782657</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7316,8 +7626,77 @@
           <t>NVI Aros Park</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107678937</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>